--- a/data/nzd0024/nzd0024.xlsx
+++ b/data/nzd0024/nzd0024.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M520"/>
+  <dimension ref="A1:M524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23850,6 +23850,186 @@
       <c r="M520" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>364.64</v>
+      </c>
+      <c r="C521" t="n">
+        <v>375.87</v>
+      </c>
+      <c r="D521" t="n">
+        <v>386.2</v>
+      </c>
+      <c r="E521" t="n">
+        <v>389.42</v>
+      </c>
+      <c r="F521" t="n">
+        <v>391.05</v>
+      </c>
+      <c r="G521" t="n">
+        <v>387.53</v>
+      </c>
+      <c r="H521" t="n">
+        <v>383.68</v>
+      </c>
+      <c r="I521" t="n">
+        <v>386.71</v>
+      </c>
+      <c r="J521" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="K521" t="n">
+        <v>396.17</v>
+      </c>
+      <c r="L521" t="n">
+        <v>398.18</v>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>363.06</v>
+      </c>
+      <c r="C522" t="n">
+        <v>374.59</v>
+      </c>
+      <c r="D522" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="E522" t="n">
+        <v>388.3</v>
+      </c>
+      <c r="F522" t="n">
+        <v>390.86</v>
+      </c>
+      <c r="G522" t="n">
+        <v>388.17</v>
+      </c>
+      <c r="H522" t="n">
+        <v>383.7</v>
+      </c>
+      <c r="I522" t="n">
+        <v>387.16</v>
+      </c>
+      <c r="J522" t="n">
+        <v>390.82</v>
+      </c>
+      <c r="K522" t="n">
+        <v>396.57</v>
+      </c>
+      <c r="L522" t="n">
+        <v>398.31</v>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>362.31</v>
+      </c>
+      <c r="C523" t="n">
+        <v>374.89</v>
+      </c>
+      <c r="D523" t="n">
+        <v>385.16</v>
+      </c>
+      <c r="E523" t="n">
+        <v>387.89</v>
+      </c>
+      <c r="F523" t="n">
+        <v>390.12</v>
+      </c>
+      <c r="G523" t="n">
+        <v>387.51</v>
+      </c>
+      <c r="H523" t="n">
+        <v>383.42</v>
+      </c>
+      <c r="I523" t="n">
+        <v>386.99</v>
+      </c>
+      <c r="J523" t="n">
+        <v>390.61</v>
+      </c>
+      <c r="K523" t="n">
+        <v>396.01</v>
+      </c>
+      <c r="L523" t="n">
+        <v>397.94</v>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>361.76</v>
+      </c>
+      <c r="C524" t="n">
+        <v>375.16</v>
+      </c>
+      <c r="D524" t="n">
+        <v>384.89</v>
+      </c>
+      <c r="E524" t="n">
+        <v>387.45</v>
+      </c>
+      <c r="F524" t="n">
+        <v>389.75</v>
+      </c>
+      <c r="G524" t="n">
+        <v>387.23</v>
+      </c>
+      <c r="H524" t="n">
+        <v>383.31</v>
+      </c>
+      <c r="I524" t="n">
+        <v>387.13</v>
+      </c>
+      <c r="J524" t="n">
+        <v>390.55</v>
+      </c>
+      <c r="K524" t="n">
+        <v>395.86</v>
+      </c>
+      <c r="L524" t="n">
+        <v>397.92</v>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23864,7 +24044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B603"/>
+  <dimension ref="A1:B607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29897,6 +30077,46 @@
       </c>
       <c r="B603" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>-0.89</v>
       </c>
     </row>
   </sheetData>
@@ -30065,28 +30285,28 @@
         <v>0.0737</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05815322646787028</v>
+        <v>0.04093162690061376</v>
       </c>
       <c r="J2" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K2" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005417220447415216</v>
+        <v>0.002663609941495726</v>
       </c>
       <c r="M2" t="n">
-        <v>4.911867141637939</v>
+        <v>4.962534415884812</v>
       </c>
       <c r="N2" t="n">
-        <v>37.20719971409083</v>
+        <v>37.95757923508562</v>
       </c>
       <c r="O2" t="n">
-        <v>6.099770464049514</v>
+        <v>6.160972263781556</v>
       </c>
       <c r="P2" t="n">
-        <v>373.1051943057508</v>
+        <v>373.2794835365036</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30143,28 +30363,28 @@
         <v>0.0822</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09269911458486363</v>
+        <v>0.08442879163290011</v>
       </c>
       <c r="J3" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K3" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01942057558889532</v>
+        <v>0.01629334303144048</v>
       </c>
       <c r="M3" t="n">
-        <v>4.001156789406768</v>
+        <v>4.018578376009043</v>
       </c>
       <c r="N3" t="n">
-        <v>26.00080409341336</v>
+        <v>26.04030171207312</v>
       </c>
       <c r="O3" t="n">
-        <v>5.099098360829428</v>
+        <v>5.102969891354751</v>
       </c>
       <c r="P3" t="n">
-        <v>378.2615349489321</v>
+        <v>378.3452308832865</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30221,28 +30441,28 @@
         <v>0.0805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09507686284673172</v>
+        <v>0.09133488313089895</v>
       </c>
       <c r="J4" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K4" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01639906831262605</v>
+        <v>0.01539004047452575</v>
       </c>
       <c r="M4" t="n">
-        <v>4.575095224898786</v>
+        <v>4.559479298009344</v>
       </c>
       <c r="N4" t="n">
-        <v>32.49109675186318</v>
+        <v>32.29291671688864</v>
       </c>
       <c r="O4" t="n">
-        <v>5.700096205491902</v>
+        <v>5.682685695768211</v>
       </c>
       <c r="P4" t="n">
-        <v>385.4464014509854</v>
+        <v>385.4842747917035</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30299,28 +30519,28 @@
         <v>0.0893</v>
       </c>
       <c r="I5" t="n">
-        <v>0.142960934615131</v>
+        <v>0.1363487152125607</v>
       </c>
       <c r="J5" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K5" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03269723231967514</v>
+        <v>0.03020997200538811</v>
       </c>
       <c r="M5" t="n">
-        <v>4.800024666399662</v>
+        <v>4.799976453402873</v>
       </c>
       <c r="N5" t="n">
-        <v>36.23273545453888</v>
+        <v>36.11095272008434</v>
       </c>
       <c r="O5" t="n">
-        <v>6.019363376183471</v>
+        <v>6.00923894682882</v>
       </c>
       <c r="P5" t="n">
-        <v>388.9137148099099</v>
+        <v>388.9806365646011</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30377,28 +30597,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2406358575195141</v>
+        <v>0.2323456012145039</v>
       </c>
       <c r="J6" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K6" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08553236850991019</v>
+        <v>0.08100835814148566</v>
       </c>
       <c r="M6" t="n">
-        <v>5.083873000828252</v>
+        <v>5.087407699236604</v>
       </c>
       <c r="N6" t="n">
-        <v>37.09996100253642</v>
+        <v>37.05613298985475</v>
       </c>
       <c r="O6" t="n">
-        <v>6.090973731886916</v>
+        <v>6.087374884944638</v>
       </c>
       <c r="P6" t="n">
-        <v>389.6056495190303</v>
+        <v>389.6895500398837</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30455,28 +30675,28 @@
         <v>0.0825</v>
       </c>
       <c r="I7" t="n">
-        <v>0.134500852479588</v>
+        <v>0.1273931994407356</v>
       </c>
       <c r="J7" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K7" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02295475570833816</v>
+        <v>0.02091634731238523</v>
       </c>
       <c r="M7" t="n">
-        <v>5.613706462159834</v>
+        <v>5.599275528080804</v>
       </c>
       <c r="N7" t="n">
-        <v>46.14312486945801</v>
+        <v>45.96591397542362</v>
       </c>
       <c r="O7" t="n">
-        <v>6.792873093872577</v>
+        <v>6.779816662375437</v>
       </c>
       <c r="P7" t="n">
-        <v>388.8287113805496</v>
+        <v>388.9006401108924</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30533,28 +30753,28 @@
         <v>0.1961</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2505671424741843</v>
+        <v>0.2424448989865021</v>
       </c>
       <c r="J8" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K8" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08871431830209831</v>
+        <v>0.08440528433421313</v>
       </c>
       <c r="M8" t="n">
-        <v>4.943492345236061</v>
+        <v>4.937631396824314</v>
       </c>
       <c r="N8" t="n">
-        <v>38.64773046449727</v>
+        <v>38.58061956249151</v>
       </c>
       <c r="O8" t="n">
-        <v>6.216729885116232</v>
+        <v>6.211329935085682</v>
       </c>
       <c r="P8" t="n">
-        <v>382.3076291676984</v>
+        <v>382.3898253362976</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30611,28 +30831,28 @@
         <v>0.1295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.271911182007769</v>
+        <v>0.2623988551001279</v>
       </c>
       <c r="J9" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K9" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07715321658218488</v>
+        <v>0.07300000012002139</v>
       </c>
       <c r="M9" t="n">
-        <v>5.693138172690976</v>
+        <v>5.686845486977579</v>
       </c>
       <c r="N9" t="n">
-        <v>52.99618772442462</v>
+        <v>52.90420592298852</v>
       </c>
       <c r="O9" t="n">
-        <v>7.279848056410561</v>
+        <v>7.273527749516635</v>
       </c>
       <c r="P9" t="n">
-        <v>386.1502322244261</v>
+        <v>386.2464923803391</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30689,28 +30909,28 @@
         <v>0.1507</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1849347053028592</v>
+        <v>0.1732361243331205</v>
       </c>
       <c r="J10" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K10" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03775828130877101</v>
+        <v>0.03355249635888546</v>
       </c>
       <c r="M10" t="n">
-        <v>5.650230047383388</v>
+        <v>5.657437369469676</v>
       </c>
       <c r="N10" t="n">
-        <v>52.23044570109328</v>
+        <v>52.30459023858711</v>
       </c>
       <c r="O10" t="n">
-        <v>7.22706342168749</v>
+        <v>7.232191247373586</v>
       </c>
       <c r="P10" t="n">
-        <v>393.6426138532746</v>
+        <v>393.7610001693953</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30767,28 +30987,28 @@
         <v>0.1119</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2075829332531864</v>
+        <v>0.199452229559225</v>
       </c>
       <c r="J11" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K11" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05547476500122517</v>
+        <v>0.05202658152790585</v>
       </c>
       <c r="M11" t="n">
-        <v>5.312254762250831</v>
+        <v>5.308186363309916</v>
       </c>
       <c r="N11" t="n">
-        <v>43.96593480363041</v>
+        <v>43.85893834198465</v>
       </c>
       <c r="O11" t="n">
-        <v>6.630681322732259</v>
+        <v>6.622608122332519</v>
       </c>
       <c r="P11" t="n">
-        <v>396.0956927653033</v>
+        <v>396.1779745433147</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30845,28 +31065,28 @@
         <v>0.1089</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1824116002123759</v>
+        <v>0.1697729783926274</v>
       </c>
       <c r="J12" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K12" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03826746587331553</v>
+        <v>0.03352174928189977</v>
       </c>
       <c r="M12" t="n">
-        <v>5.5953257569572</v>
+        <v>5.607878399993075</v>
       </c>
       <c r="N12" t="n">
-        <v>50.11231189633239</v>
+        <v>50.28193733338109</v>
       </c>
       <c r="O12" t="n">
-        <v>7.079005007508639</v>
+        <v>7.090975767366653</v>
       </c>
       <c r="P12" t="n">
-        <v>401.7788914157231</v>
+        <v>401.9067915536949</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30904,7 +31124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M520"/>
+  <dimension ref="A1:M524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65747,6 +65967,274 @@
         </is>
       </c>
     </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-34.82202250024789,173.40817310723435</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-34.822642364094996,173.40770500014548</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-34.82330750026506,173.40741039659466</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-34.82399106651168,173.40720379613813</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>-34.82469196598679,173.4070852054605</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>-34.82540148180943,173.40702189430073</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>-34.82612660515316,173.40702288422378</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>-34.82682737698099,173.40714371227293</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>-34.82745351316129,173.40745364473293</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>-34.82793629686062,173.4079902481123</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>-34.82831092683212,173.4086948952833</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-34.822013447341284,173.40815976602363</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-34.82263602312441,173.40769330464664</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>-34.823305507026056,173.40740429701137</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>-34.823988883566955,173.40719183826565</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>-34.82469181071362,173.40708313631336</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>-34.82540140888934,173.40702889236022</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>-34.82612659095154,173.4070231022534</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>-34.826826483526624,173.40714851249993</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>-34.82745277818684,173.4074552761907</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>-34.82793367341425,173.4079932501791</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>-34.82830996260849,173.40869570382455</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-34.822009150074976,173.40815343317144</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-34.8226375092895,173.40769604577903</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>-34.82330404531727,173.4073998239838</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>-34.82398808445298,173.40718746083033</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>-34.8246912059652,173.4070750775298</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>-34.825401484088175,173.4070216756114</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>-34.82612678977401,173.40702004983885</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>-34.82682682105385,173.40714669908084</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>-34.827453686096455,173.40745326086048</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>-34.827937346239146,173.4079890472855</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>-34.82831270693724,173.4086934025917</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-34.822005998746135,173.40814878908026</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-34.82263884683802,173.40769851279825</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-34.82330314835953,173.4073970791715</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-34.82398722686706,173.40718276309497</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>-34.824690903590785,173.40707104813808</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>-34.82540151599059,173.4070186139604</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>-34.82612686788281,173.40701885067597</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>-34.826826543090256,173.4071481924848</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>-34.827453945499194,173.40745268505185</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>-34.8279383300315,173.40798792151037</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>-34.828312855279336,173.40869327820073</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0024/nzd0024.xlsx
+++ b/data/nzd0024/nzd0024.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M524"/>
+  <dimension ref="A1:M529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24030,6 +24030,231 @@
       <c r="M524" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>360.23</v>
+      </c>
+      <c r="C525" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="D525" t="n">
+        <v>384.27</v>
+      </c>
+      <c r="E525" t="n">
+        <v>387.22</v>
+      </c>
+      <c r="F525" t="n">
+        <v>388.79</v>
+      </c>
+      <c r="G525" t="n">
+        <v>387.01</v>
+      </c>
+      <c r="H525" t="n">
+        <v>383.17</v>
+      </c>
+      <c r="I525" t="n">
+        <v>386.85</v>
+      </c>
+      <c r="J525" t="n">
+        <v>390.27</v>
+      </c>
+      <c r="K525" t="n">
+        <v>395.46</v>
+      </c>
+      <c r="L525" t="n">
+        <v>397.81</v>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>361.7</v>
+      </c>
+      <c r="C526" t="n">
+        <v>374.91</v>
+      </c>
+      <c r="D526" t="n">
+        <v>385.06</v>
+      </c>
+      <c r="E526" t="n">
+        <v>387.62</v>
+      </c>
+      <c r="F526" t="n">
+        <v>389.46</v>
+      </c>
+      <c r="G526" t="n">
+        <v>387.48</v>
+      </c>
+      <c r="H526" t="n">
+        <v>383.61</v>
+      </c>
+      <c r="I526" t="n">
+        <v>387.1</v>
+      </c>
+      <c r="J526" t="n">
+        <v>390.86</v>
+      </c>
+      <c r="K526" t="n">
+        <v>395.87</v>
+      </c>
+      <c r="L526" t="n">
+        <v>397.85</v>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>361.51</v>
+      </c>
+      <c r="C527" t="n">
+        <v>374.91</v>
+      </c>
+      <c r="D527" t="n">
+        <v>383</v>
+      </c>
+      <c r="E527" t="n">
+        <v>386.03</v>
+      </c>
+      <c r="F527" t="n">
+        <v>390.27</v>
+      </c>
+      <c r="G527" t="n">
+        <v>387.91</v>
+      </c>
+      <c r="H527" t="n">
+        <v>383.61</v>
+      </c>
+      <c r="I527" t="n">
+        <v>386.26</v>
+      </c>
+      <c r="J527" t="n">
+        <v>391.78</v>
+      </c>
+      <c r="K527" t="n">
+        <v>395.87</v>
+      </c>
+      <c r="L527" t="n">
+        <v>397.85</v>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>360.99</v>
+      </c>
+      <c r="C528" t="n">
+        <v>374.44</v>
+      </c>
+      <c r="D528" t="n">
+        <v>382.05</v>
+      </c>
+      <c r="E528" t="n">
+        <v>385.61</v>
+      </c>
+      <c r="F528" t="n">
+        <v>389.38</v>
+      </c>
+      <c r="G528" t="n">
+        <v>387.66</v>
+      </c>
+      <c r="H528" t="n">
+        <v>383.41</v>
+      </c>
+      <c r="I528" t="n">
+        <v>386</v>
+      </c>
+      <c r="J528" t="n">
+        <v>391.6</v>
+      </c>
+      <c r="K528" t="n">
+        <v>395.7</v>
+      </c>
+      <c r="L528" t="n">
+        <v>397.53</v>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>362.15</v>
+      </c>
+      <c r="C529" t="n">
+        <v>375.36</v>
+      </c>
+      <c r="D529" t="n">
+        <v>382.52</v>
+      </c>
+      <c r="E529" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="F529" t="n">
+        <v>389.52</v>
+      </c>
+      <c r="G529" t="n">
+        <v>387.91</v>
+      </c>
+      <c r="H529" t="n">
+        <v>383.54</v>
+      </c>
+      <c r="I529" t="n">
+        <v>386.57</v>
+      </c>
+      <c r="J529" t="n">
+        <v>391.88</v>
+      </c>
+      <c r="K529" t="n">
+        <v>395.96</v>
+      </c>
+      <c r="L529" t="n">
+        <v>397.34</v>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -24044,7 +24269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B607"/>
+  <dimension ref="A1:B612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30117,6 +30342,56 @@
       </c>
       <c r="B607" t="n">
         <v>-0.89</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -30285,28 +30560,28 @@
         <v>0.0737</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04093162690061376</v>
+        <v>0.01746088604326633</v>
       </c>
       <c r="J2" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K2" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002663609941495726</v>
+        <v>0.0004762920551426575</v>
       </c>
       <c r="M2" t="n">
-        <v>4.962534415884812</v>
+        <v>5.040826253755559</v>
       </c>
       <c r="N2" t="n">
-        <v>37.95757923508562</v>
+        <v>39.17121030344727</v>
       </c>
       <c r="O2" t="n">
-        <v>6.160972263781556</v>
+        <v>6.258690781900579</v>
       </c>
       <c r="P2" t="n">
-        <v>373.2794835365036</v>
+        <v>373.5180826650176</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30363,28 +30638,28 @@
         <v>0.0822</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08442879163290011</v>
+        <v>0.07368108188643561</v>
       </c>
       <c r="J3" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K3" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01629334303144048</v>
+        <v>0.01256211390538087</v>
       </c>
       <c r="M3" t="n">
-        <v>4.018578376009043</v>
+        <v>4.043806833339836</v>
       </c>
       <c r="N3" t="n">
-        <v>26.04030171207312</v>
+        <v>26.12604795288782</v>
       </c>
       <c r="O3" t="n">
-        <v>5.102969891354751</v>
+        <v>5.11136458813963</v>
       </c>
       <c r="P3" t="n">
-        <v>378.3452308832865</v>
+        <v>378.4544872653404</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30441,28 +30716,28 @@
         <v>0.0805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09133488313089895</v>
+        <v>0.08311656796315921</v>
       </c>
       <c r="J4" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K4" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01539004047452575</v>
+        <v>0.01296831506189156</v>
       </c>
       <c r="M4" t="n">
-        <v>4.559479298009344</v>
+        <v>4.558094117303672</v>
       </c>
       <c r="N4" t="n">
-        <v>32.29291671688864</v>
+        <v>32.19121862256348</v>
       </c>
       <c r="O4" t="n">
-        <v>5.682685695768211</v>
+        <v>5.673730573666984</v>
       </c>
       <c r="P4" t="n">
-        <v>385.4842747917035</v>
+        <v>385.5678392244998</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30519,28 +30794,28 @@
         <v>0.0893</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1363487152125607</v>
+        <v>0.1252421452930936</v>
       </c>
       <c r="J5" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K5" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03020997200538811</v>
+        <v>0.02589415170363085</v>
       </c>
       <c r="M5" t="n">
-        <v>4.799976453402873</v>
+        <v>4.815211964375256</v>
       </c>
       <c r="N5" t="n">
-        <v>36.11095272008434</v>
+        <v>36.12602108279366</v>
       </c>
       <c r="O5" t="n">
-        <v>6.00923894682882</v>
+        <v>6.010492582375729</v>
       </c>
       <c r="P5" t="n">
-        <v>388.9806365646011</v>
+        <v>389.0935579134194</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30597,28 +30872,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2323456012145039</v>
+        <v>0.2206887763255999</v>
       </c>
       <c r="J6" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K6" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08100835814148566</v>
+        <v>0.07440287775353704</v>
       </c>
       <c r="M6" t="n">
-        <v>5.087407699236604</v>
+        <v>5.098532359867148</v>
       </c>
       <c r="N6" t="n">
-        <v>37.05613298985475</v>
+        <v>37.09432113876977</v>
       </c>
       <c r="O6" t="n">
-        <v>6.087374884944638</v>
+        <v>6.090510745312725</v>
       </c>
       <c r="P6" t="n">
-        <v>389.6895500398837</v>
+        <v>389.8080510081735</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30675,28 +30950,28 @@
         <v>0.0825</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1273931994407356</v>
+        <v>0.1188582062577261</v>
       </c>
       <c r="J7" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K7" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02091634731238523</v>
+        <v>0.01855876250907895</v>
       </c>
       <c r="M7" t="n">
-        <v>5.599275528080804</v>
+        <v>5.580840667898132</v>
       </c>
       <c r="N7" t="n">
-        <v>45.96591397542362</v>
+        <v>45.73917252188504</v>
       </c>
       <c r="O7" t="n">
-        <v>6.779816662375437</v>
+        <v>6.763074191659074</v>
       </c>
       <c r="P7" t="n">
-        <v>388.9006401108924</v>
+        <v>388.9874030026789</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30753,28 +31028,28 @@
         <v>0.1961</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2424448989865021</v>
+        <v>0.2326050875699356</v>
       </c>
       <c r="J8" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K8" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08440528433421313</v>
+        <v>0.07923877598134887</v>
       </c>
       <c r="M8" t="n">
-        <v>4.937631396824314</v>
+        <v>4.929328053405004</v>
       </c>
       <c r="N8" t="n">
-        <v>38.58061956249151</v>
+        <v>38.49128007150574</v>
       </c>
       <c r="O8" t="n">
-        <v>6.211329935085682</v>
+        <v>6.204134111341062</v>
       </c>
       <c r="P8" t="n">
-        <v>382.3898253362976</v>
+        <v>382.4898563874982</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30831,28 +31106,28 @@
         <v>0.1295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2623988551001279</v>
+        <v>0.2502124680550418</v>
       </c>
       <c r="J9" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K9" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07300000012002139</v>
+        <v>0.06764753085520014</v>
       </c>
       <c r="M9" t="n">
-        <v>5.686845486977579</v>
+        <v>5.680102864490888</v>
       </c>
       <c r="N9" t="n">
-        <v>52.90420592298852</v>
+        <v>52.82758305209665</v>
       </c>
       <c r="O9" t="n">
-        <v>7.273527749516635</v>
+        <v>7.26825859832303</v>
       </c>
       <c r="P9" t="n">
-        <v>386.2464923803391</v>
+        <v>386.3703843696611</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30909,28 +31184,28 @@
         <v>0.1507</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1732361243331205</v>
+        <v>0.160369646567621</v>
       </c>
       <c r="J10" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K10" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03355249635888546</v>
+        <v>0.02923484309028612</v>
       </c>
       <c r="M10" t="n">
-        <v>5.657437369469676</v>
+        <v>5.658812702947724</v>
       </c>
       <c r="N10" t="n">
-        <v>52.30459023858711</v>
+        <v>52.28443618340368</v>
       </c>
       <c r="O10" t="n">
-        <v>7.232191247373586</v>
+        <v>7.230797755670095</v>
       </c>
       <c r="P10" t="n">
-        <v>393.7610001693953</v>
+        <v>393.8917924433612</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30987,28 +31262,28 @@
         <v>0.1119</v>
       </c>
       <c r="I11" t="n">
-        <v>0.199452229559225</v>
+        <v>0.18903434326545</v>
       </c>
       <c r="J11" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K11" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05202658152790585</v>
+        <v>0.0476209572112668</v>
       </c>
       <c r="M11" t="n">
-        <v>5.308186363309916</v>
+        <v>5.304579652584037</v>
       </c>
       <c r="N11" t="n">
-        <v>43.85893834198465</v>
+        <v>43.75299703970495</v>
       </c>
       <c r="O11" t="n">
-        <v>6.622608122332519</v>
+        <v>6.614604828688178</v>
       </c>
       <c r="P11" t="n">
-        <v>396.1779745433147</v>
+        <v>396.283881715283</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31065,28 +31340,28 @@
         <v>0.1089</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1697729783926274</v>
+        <v>0.1539257362228799</v>
       </c>
       <c r="J12" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K12" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03352174928189977</v>
+        <v>0.02791055555492727</v>
       </c>
       <c r="M12" t="n">
-        <v>5.607878399993075</v>
+        <v>5.624585147409694</v>
       </c>
       <c r="N12" t="n">
-        <v>50.28193733338109</v>
+        <v>50.52134421553859</v>
       </c>
       <c r="O12" t="n">
-        <v>7.090975767366653</v>
+        <v>7.107836816890114</v>
       </c>
       <c r="P12" t="n">
-        <v>401.9067915536949</v>
+        <v>402.0678978478431</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31124,7 +31399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M524"/>
+  <dimension ref="A1:M529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66235,6 +66510,341 @@
         </is>
       </c>
     </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-34.821997232321294,173.40813587006483</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-34.82263116831804,173.40768435028156</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-34.82330108867853,173.4073907762694</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-34.82398677858343,173.4071803074606</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-34.82469011905116,173.4070605935002</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-34.82540154105673,173.4070162083774</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>-34.826126967294016,173.4070173244687</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>-34.82682709901742,173.4071452056769</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>-34.82745515604529,173.4074499979448</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>-34.82794095347772,173.4079849194432</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>-34.828313671160856,173.4086925940504</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-34.8220056549648,173.40814828245215</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-34.82263760836716,173.4076962285212</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-34.82330371311071,173.40739880738664</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-34.823987558207094,173.4071845781291</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>-34.824690666594535,173.4070678899662</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>-34.8254014875063,173.40702134757734</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>-34.826126654858776,173.40702212112015</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>-34.82682660265388,173.40714787246966</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>-34.827452605251665,173.4074556600631</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>-34.827938264445336,173.40798799656204</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>-34.82831337447667,173.40869284283232</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-34.82200456632387,173.40814667812984</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-34.82263760836716,173.4076962285212</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-34.82329686965353,173.40737786548712</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-34.82398445920217,173.40716760222242</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>-34.82469132854938,173.40707671106702</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>-34.825401438513175,173.40702604939855</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>-34.826126654858776,173.40702212112015</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>-34.82682827043516,173.4071389120458</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>-34.82744862774244,173.40746448912816</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>-34.827938264445336,173.40798799656204</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>-34.82831337447667,173.40869284283232</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-34.82200158688545,173.4081422873532</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-34.822635280041844,173.4076919340805</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>-34.82329371368905,173.40736820781615</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-34.823983640596694,173.40716311802086</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>-34.824690601216254,173.40706701874637</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>-34.825401466997576,173.4070233157816</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>-34.82612679687482,173.40701994082406</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>-34.826828786653046,173.40713613858122</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>-34.82744940595082,173.40746276170245</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>-34.82793937940999,173.4079867206835</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>-34.828315747950136,173.40869085257674</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>-34.82200823332479,173.40815208216307</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>-34.822639837614666,173.40770034021995</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>-34.82329527506105,173.40737298582167</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-34.82398428378673,173.40716664132205</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>-34.82469071562825,173.40706854338106</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>-34.825401438513175,173.40702604939855</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>-34.8261267045644,173.40702135801652</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>-34.82682765494452,173.40714221886896</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>-34.82744819540444,173.40746544880912</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>-34.82793767416994,173.40798867202713</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>-34.828317157200004,173.4086896708624</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0024/nzd0024.xlsx
+++ b/data/nzd0024/nzd0024.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M529"/>
+  <dimension ref="A1:M532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24253,6 +24253,141 @@
         <v>397.34</v>
       </c>
       <c r="M529" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>361.82</v>
+      </c>
+      <c r="C530" t="n">
+        <v>374.9</v>
+      </c>
+      <c r="D530" t="n">
+        <v>381.8</v>
+      </c>
+      <c r="E530" t="n">
+        <v>385.58</v>
+      </c>
+      <c r="F530" t="n">
+        <v>388.88</v>
+      </c>
+      <c r="G530" t="n">
+        <v>387.33</v>
+      </c>
+      <c r="H530" t="n">
+        <v>383.43</v>
+      </c>
+      <c r="I530" t="n">
+        <v>386.53</v>
+      </c>
+      <c r="J530" t="n">
+        <v>391.51</v>
+      </c>
+      <c r="K530" t="n">
+        <v>395.72</v>
+      </c>
+      <c r="L530" t="n">
+        <v>396.84</v>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>363.17</v>
+      </c>
+      <c r="C531" t="n">
+        <v>375.49</v>
+      </c>
+      <c r="D531" t="n">
+        <v>382.3</v>
+      </c>
+      <c r="E531" t="n">
+        <v>386.27</v>
+      </c>
+      <c r="F531" t="n">
+        <v>389.22</v>
+      </c>
+      <c r="G531" t="n">
+        <v>387.43</v>
+      </c>
+      <c r="H531" t="n">
+        <v>383.75</v>
+      </c>
+      <c r="I531" t="n">
+        <v>387.22</v>
+      </c>
+      <c r="J531" t="n">
+        <v>392.13</v>
+      </c>
+      <c r="K531" t="n">
+        <v>395.97</v>
+      </c>
+      <c r="L531" t="n">
+        <v>397.29</v>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>365.08</v>
+      </c>
+      <c r="C532" t="n">
+        <v>376.42</v>
+      </c>
+      <c r="D532" t="n">
+        <v>383.47</v>
+      </c>
+      <c r="E532" t="n">
+        <v>387.31</v>
+      </c>
+      <c r="F532" t="n">
+        <v>389.99</v>
+      </c>
+      <c r="G532" t="n">
+        <v>388.09</v>
+      </c>
+      <c r="H532" t="n">
+        <v>384.09</v>
+      </c>
+      <c r="I532" t="n">
+        <v>387.59</v>
+      </c>
+      <c r="J532" t="n">
+        <v>392.67</v>
+      </c>
+      <c r="K532" t="n">
+        <v>396.4</v>
+      </c>
+      <c r="L532" t="n">
+        <v>397.53</v>
+      </c>
+      <c r="M532" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24269,7 +24404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30392,6 +30527,36 @@
       </c>
       <c r="B612" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -30560,28 +30725,28 @@
         <v>0.0737</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01746088604326633</v>
+        <v>0.006130278858873475</v>
       </c>
       <c r="J2" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K2" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004762920551426575</v>
+        <v>5.85168841917838e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>5.040826253755559</v>
+        <v>5.075684377732433</v>
       </c>
       <c r="N2" t="n">
-        <v>39.17121030344727</v>
+        <v>39.58731989452676</v>
       </c>
       <c r="O2" t="n">
-        <v>6.258690781900579</v>
+        <v>6.291845507840029</v>
       </c>
       <c r="P2" t="n">
-        <v>373.5180826650176</v>
+        <v>373.6336954768803</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30638,28 +30803,28 @@
         <v>0.0822</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07368108188643561</v>
+        <v>0.06851108072379587</v>
       </c>
       <c r="J3" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K3" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01256211390538087</v>
+        <v>0.01095999435987993</v>
       </c>
       <c r="M3" t="n">
-        <v>4.043806833339836</v>
+        <v>4.051104228241735</v>
       </c>
       <c r="N3" t="n">
-        <v>26.12604795288782</v>
+        <v>26.11123491770876</v>
       </c>
       <c r="O3" t="n">
-        <v>5.11136458813963</v>
+        <v>5.109915353282162</v>
       </c>
       <c r="P3" t="n">
-        <v>378.4544872653404</v>
+        <v>378.5072395529198</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30716,28 +30881,28 @@
         <v>0.0805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08311656796315921</v>
+        <v>0.07746834696632598</v>
       </c>
       <c r="J4" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K4" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01296831506189156</v>
+        <v>0.01136999777306869</v>
       </c>
       <c r="M4" t="n">
-        <v>4.558094117303672</v>
+        <v>4.560780054540156</v>
       </c>
       <c r="N4" t="n">
-        <v>32.19121862256348</v>
+        <v>32.16801271187089</v>
       </c>
       <c r="O4" t="n">
-        <v>5.673730573666984</v>
+        <v>5.671685173902981</v>
       </c>
       <c r="P4" t="n">
-        <v>385.5678392244998</v>
+        <v>385.6254704549642</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30794,28 +30959,28 @@
         <v>0.0893</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1252421452930936</v>
+        <v>0.1187349102733093</v>
       </c>
       <c r="J5" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K5" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02589415170363085</v>
+        <v>0.02348815825667716</v>
       </c>
       <c r="M5" t="n">
-        <v>4.815211964375256</v>
+        <v>4.823154626774759</v>
       </c>
       <c r="N5" t="n">
-        <v>36.12602108279366</v>
+        <v>36.13163828783832</v>
       </c>
       <c r="O5" t="n">
-        <v>6.010492582375729</v>
+        <v>6.010959847465156</v>
       </c>
       <c r="P5" t="n">
-        <v>389.0935579134194</v>
+        <v>389.1599558393755</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30872,28 +31037,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2206887763255999</v>
+        <v>0.2138334989367873</v>
       </c>
       <c r="J6" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K6" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07440287775353704</v>
+        <v>0.07058432131853842</v>
       </c>
       <c r="M6" t="n">
-        <v>5.098532359867148</v>
+        <v>5.104580686514024</v>
       </c>
       <c r="N6" t="n">
-        <v>37.09432113876977</v>
+        <v>37.11551433513906</v>
       </c>
       <c r="O6" t="n">
-        <v>6.090510745312725</v>
+        <v>6.09225035066182</v>
       </c>
       <c r="P6" t="n">
-        <v>389.8080510081735</v>
+        <v>389.8780039297176</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30950,28 +31115,28 @@
         <v>0.0825</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1188582062577261</v>
+        <v>0.1139585875677446</v>
       </c>
       <c r="J7" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K7" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01855876250907895</v>
+        <v>0.01725383736002806</v>
       </c>
       <c r="M7" t="n">
-        <v>5.580840667898132</v>
+        <v>5.56908920966363</v>
       </c>
       <c r="N7" t="n">
-        <v>45.73917252188504</v>
+        <v>45.59865364528196</v>
       </c>
       <c r="O7" t="n">
-        <v>6.763074191659074</v>
+        <v>6.752677516754518</v>
       </c>
       <c r="P7" t="n">
-        <v>388.9874030026789</v>
+        <v>389.0373997076416</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31028,28 +31193,28 @@
         <v>0.1961</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2326050875699356</v>
+        <v>0.2272266514356545</v>
       </c>
       <c r="J8" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K8" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07923877598134887</v>
+        <v>0.07651459863170185</v>
       </c>
       <c r="M8" t="n">
-        <v>4.929328053405004</v>
+        <v>4.922371929744659</v>
       </c>
       <c r="N8" t="n">
-        <v>38.49128007150574</v>
+        <v>38.41550213211745</v>
       </c>
       <c r="O8" t="n">
-        <v>6.204134111341062</v>
+        <v>6.198024050624316</v>
       </c>
       <c r="P8" t="n">
-        <v>382.4898563874982</v>
+        <v>382.5447409440413</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31106,28 +31271,28 @@
         <v>0.1295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2502124680550418</v>
+        <v>0.2437678723394107</v>
       </c>
       <c r="J9" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K9" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06764753085520014</v>
+        <v>0.06495390938474677</v>
       </c>
       <c r="M9" t="n">
-        <v>5.680102864490888</v>
+        <v>5.672719517095762</v>
       </c>
       <c r="N9" t="n">
-        <v>52.82758305209665</v>
+        <v>52.73305163758045</v>
       </c>
       <c r="O9" t="n">
-        <v>7.26825859832303</v>
+        <v>7.261752656045265</v>
       </c>
       <c r="P9" t="n">
-        <v>386.3703843696611</v>
+        <v>386.4361477395399</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31184,28 +31349,28 @@
         <v>0.1507</v>
       </c>
       <c r="I10" t="n">
-        <v>0.160369646567621</v>
+        <v>0.1538251678975623</v>
       </c>
       <c r="J10" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K10" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02923484309028612</v>
+        <v>0.02718447749227182</v>
       </c>
       <c r="M10" t="n">
-        <v>5.658812702947724</v>
+        <v>5.654542904054067</v>
       </c>
       <c r="N10" t="n">
-        <v>52.28443618340368</v>
+        <v>52.19952423316563</v>
       </c>
       <c r="O10" t="n">
-        <v>7.230797755670095</v>
+        <v>7.224923821962806</v>
       </c>
       <c r="P10" t="n">
-        <v>393.8917924433612</v>
+        <v>393.958574168409</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31262,28 +31427,28 @@
         <v>0.1119</v>
       </c>
       <c r="I11" t="n">
-        <v>0.18903434326545</v>
+        <v>0.1832959748041287</v>
       </c>
       <c r="J11" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K11" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0476209572112668</v>
+        <v>0.04528234341229032</v>
       </c>
       <c r="M11" t="n">
-        <v>5.304579652584037</v>
+        <v>5.300200155150717</v>
       </c>
       <c r="N11" t="n">
-        <v>43.75299703970495</v>
+        <v>43.66708119625461</v>
       </c>
       <c r="O11" t="n">
-        <v>6.614604828688178</v>
+        <v>6.608107232502709</v>
       </c>
       <c r="P11" t="n">
-        <v>396.283881715283</v>
+        <v>396.3424390551282</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31340,28 +31505,28 @@
         <v>0.1089</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1539257362228799</v>
+        <v>0.1443052209786036</v>
       </c>
       <c r="J12" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K12" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02791055555492727</v>
+        <v>0.02469995300581718</v>
       </c>
       <c r="M12" t="n">
-        <v>5.624585147409694</v>
+        <v>5.634901258253421</v>
       </c>
       <c r="N12" t="n">
-        <v>50.52134421553859</v>
+        <v>50.6883849617937</v>
       </c>
       <c r="O12" t="n">
-        <v>7.107836816890114</v>
+        <v>7.11957758310096</v>
       </c>
       <c r="P12" t="n">
-        <v>402.0678978478431</v>
+        <v>402.1660738579319</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31399,7 +31564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M529"/>
+  <dimension ref="A1:M532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66845,6 +67010,207 @@
         </is>
       </c>
     </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>-34.82200634252747,173.40814929570837</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>-34.82263755882834,173.4076961371501</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>-34.82329288317195,173.4073656663239</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>-34.82398358212487,173.40716279772073</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>-34.824690192601786,173.4070615736225</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>-34.82540150459689,173.40701970740716</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>-34.826126782673214,173.40702015885367</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>-34.82682773436268,173.4071417921821</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>-34.827449795054996,173.4074618979896</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>-34.82793924823769,173.40798687078686</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>-34.82832086575221,173.40868656108768</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>-34.822014077606994,173.408160694842</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>-34.82264048161949,173.40770152804407</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>-34.8232945442061,173.40737074930843</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>-34.82398492697665,173.40717016462332</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>-34.82469047045964,173.40706527630672</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>-34.82540149320317,173.40702080085396</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>-34.826126555447516,173.4070236473274</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>-34.82682636439936,173.40714915253017</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>-34.82744711455942,173.4074678480114</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>-34.82793760858377,173.4079887470788</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>-34.82831752805523,173.40868935988493</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>-34.82202502131023,173.40817682250872</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>-34.822645088730454,173.40771002555567</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>-34.82329843102515,173.407382643493</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>-34.82398695399876,173.407181268361</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-34.82469109972556,173.4070736617976</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>-34.82540141800437,173.40702801760278</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>-34.82612631402011,173.40702735383078</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>-34.82682562978117,173.4071530993834</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>-34.827444779934005,173.40747303028814</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>-34.82793478837897,173.40799197430073</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>-34.828315747950136,173.40869085257674</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
